--- a/dataset_t6_grouped/results2/G4/G4_T5177_W0015F0001T0006Z000C1N60_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T5177_W0015F0001T0006Z000C1N60_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>55.08501345428608</v>
+        <v>8.951314686321489</v>
       </c>
       <c r="D2" t="n">
-        <v>28.24582237831593</v>
+        <v>4.589946136476338</v>
       </c>
       <c r="E2" t="n">
-        <v>11.99406356717445</v>
+        <v>1.949035329665849</v>
       </c>
       <c r="F2" t="n">
-        <v>11.76452123531151</v>
+        <v>1.91173470073812</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>27.18954343867457</v>
+        <v>4.418300808784618</v>
       </c>
       <c r="D3" t="n">
-        <v>15.77597235897049</v>
+        <v>2.563595508332705</v>
       </c>
       <c r="E3" t="n">
-        <v>11.99406356717445</v>
+        <v>1.949035329665849</v>
       </c>
       <c r="F3" t="n">
-        <v>11.76452123531151</v>
+        <v>1.91173470073812</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>38.22265739269152</v>
+        <v>6.211181826312373</v>
       </c>
       <c r="D4" t="n">
-        <v>13.38500221715354</v>
+        <v>2.175062860287451</v>
       </c>
       <c r="E4" t="n">
-        <v>11.99406356717445</v>
+        <v>1.949035329665849</v>
       </c>
       <c r="F4" t="n">
-        <v>11.76452123531151</v>
+        <v>1.91173470073812</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>40.51723093770701</v>
+        <v>6.584050027377389</v>
       </c>
       <c r="D5" t="n">
-        <v>24.54527063154456</v>
+        <v>3.988606477625992</v>
       </c>
       <c r="E5" t="n">
-        <v>11.99406356717445</v>
+        <v>1.949035329665849</v>
       </c>
       <c r="F5" t="n">
-        <v>11.76452123531151</v>
+        <v>1.91173470073812</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>39.65650523712495</v>
+        <v>6.444182101032805</v>
       </c>
       <c r="D6" t="n">
-        <v>32.87125075152231</v>
+        <v>5.341578247122376</v>
       </c>
       <c r="E6" t="n">
-        <v>11.99406356717445</v>
+        <v>1.949035329665849</v>
       </c>
       <c r="F6" t="n">
-        <v>11.76452123531151</v>
+        <v>1.91173470073812</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>54.35406117230374</v>
+        <v>8.832534940499357</v>
       </c>
       <c r="D7" t="n">
-        <v>49.48630466026659</v>
+        <v>8.041524507293321</v>
       </c>
       <c r="E7" t="n">
-        <v>11.99406356717445</v>
+        <v>1.949035329665849</v>
       </c>
       <c r="F7" t="n">
-        <v>11.76452123531151</v>
+        <v>1.91173470073812</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>39.12194096962378</v>
+        <v>6.357315407563864</v>
       </c>
       <c r="D8" t="n">
-        <v>4.019783498414905</v>
+        <v>0.6532148184924221</v>
       </c>
       <c r="E8" t="n">
-        <v>11.99406356717445</v>
+        <v>1.949035329665849</v>
       </c>
       <c r="F8" t="n">
-        <v>11.76452123531151</v>
+        <v>1.91173470073812</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>30.12225061156074</v>
+        <v>4.894865724378621</v>
       </c>
       <c r="D9" t="n">
-        <v>24.62400345267623</v>
+        <v>4.001400561059889</v>
       </c>
       <c r="E9" t="n">
-        <v>11.99406356717445</v>
+        <v>1.949035329665849</v>
       </c>
       <c r="F9" t="n">
-        <v>11.76452123531151</v>
+        <v>1.91173470073812</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>57.37084814812097</v>
+        <v>9.322762824069658</v>
       </c>
       <c r="D10" t="n">
-        <v>32.46611227670471</v>
+        <v>5.275743244964517</v>
       </c>
       <c r="E10" t="n">
-        <v>11.99406356717445</v>
+        <v>1.949035329665849</v>
       </c>
       <c r="F10" t="n">
-        <v>11.76452123531151</v>
+        <v>1.91173470073812</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>46.92263835932474</v>
+        <v>7.624928733390271</v>
       </c>
       <c r="D11" t="n">
-        <v>26.20985062535601</v>
+        <v>4.259100726620352</v>
       </c>
       <c r="E11" t="n">
-        <v>11.99406356717445</v>
+        <v>1.949035329665849</v>
       </c>
       <c r="F11" t="n">
-        <v>11.76452123531151</v>
+        <v>1.91173470073812</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>50.58065836654889</v>
+        <v>8.219356984564195</v>
       </c>
       <c r="D12" t="n">
-        <v>40.05419471682008</v>
+        <v>6.508806641483264</v>
       </c>
       <c r="E12" t="n">
-        <v>11.99406356717445</v>
+        <v>1.949035329665849</v>
       </c>
       <c r="F12" t="n">
-        <v>11.76452123531151</v>
+        <v>1.91173470073812</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>57.31019804896956</v>
+        <v>9.312907182957554</v>
       </c>
       <c r="D13" t="n">
-        <v>33.07495912695043</v>
+        <v>5.374680858129445</v>
       </c>
       <c r="E13" t="n">
-        <v>11.99406356717445</v>
+        <v>1.949035329665849</v>
       </c>
       <c r="F13" t="n">
-        <v>11.76452123531151</v>
+        <v>1.91173470073812</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>72.12418323132336</v>
+        <v>11.72017977509005</v>
       </c>
       <c r="D14" t="n">
-        <v>40.92885052122357</v>
+        <v>6.65093820969883</v>
       </c>
       <c r="E14" t="n">
-        <v>11.99406356717445</v>
+        <v>1.949035329665849</v>
       </c>
       <c r="F14" t="n">
-        <v>11.76452123531151</v>
+        <v>1.91173470073812</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>58.40351156429478</v>
+        <v>9.490570629197903</v>
       </c>
       <c r="D15" t="n">
-        <v>39.94604485831826</v>
+        <v>6.491232289476717</v>
       </c>
       <c r="E15" t="n">
-        <v>11.99406356717445</v>
+        <v>1.949035329665849</v>
       </c>
       <c r="F15" t="n">
-        <v>11.76452123531151</v>
+        <v>1.91173470073812</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
